--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_8.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02680519679559388</v>
+        <v>0.02182351507854609</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008437736353898044</v>
+        <v>0.008432213998538026</v>
       </c>
       <c r="C2" t="n">
-        <v>50904648</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50904648</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>34976126</v>
+        <v>4105454</v>
       </c>
       <c r="L2" t="n">
-        <v>18772144</v>
+        <v>1978496</v>
       </c>
       <c r="M2" t="n">
-        <v>4430034</v>
+        <v>394347</v>
       </c>
       <c r="N2" t="n">
-        <v>209847</v>
+        <v>10411</v>
       </c>
       <c r="O2" t="n">
-        <v>2665680</v>
+        <v>226992</v>
       </c>
       <c r="P2" t="n">
-        <v>1070352</v>
+        <v>90587</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999883770942688</v>
+        <v>0.9999763369560242</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8469431400299072</v>
+        <v>0.7790477871894836</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7087403535842896</v>
+        <v>0.5967838168144226</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6331108212471008</v>
+        <v>0.4918872714042664</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2739720940589905</v>
+        <v>0.07668905705213547</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6915809512138367</v>
+        <v>0.5490750074386597</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7828994989395142</v>
+        <v>0.6785339713096619</v>
       </c>
       <c r="X2" t="n">
-        <v>50904648</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50904648</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>38791394</v>
+        <v>4813274</v>
       </c>
       <c r="AG2" t="n">
-        <v>24034613</v>
+        <v>3010697</v>
       </c>
       <c r="AH2" t="n">
-        <v>6424509</v>
+        <v>804213</v>
       </c>
       <c r="AI2" t="n">
-        <v>473880</v>
+        <v>59267</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3678844</v>
+        <v>460431</v>
       </c>
       <c r="AK2" t="n">
-        <v>1441067</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9561742544174194</v>
+        <v>0.9555724859237671</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114837646484375</v>
+        <v>0.9118132591247559</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8578961491584778</v>
+        <v>0.8582125902175903</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6616310477256775</v>
+        <v>0.6612037420272827</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019256830215454</v>
+        <v>0.9019888043403625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314501285552979</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.006817244450616774</v>
+        <v>0.005415188859594792</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002021420070486094</v>
+        <v>0.002020802637879015</v>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>34976126</v>
+        <v>4105454</v>
       </c>
       <c r="E3" t="n">
-        <v>5340023</v>
+        <v>888539</v>
       </c>
       <c r="F3" t="n">
-        <v>163789</v>
+        <v>28807</v>
       </c>
       <c r="G3" t="n">
-        <v>21188</v>
+        <v>2505</v>
       </c>
       <c r="H3" t="n">
-        <v>10032</v>
+        <v>1603</v>
       </c>
       <c r="I3" t="n">
-        <v>712</v>
+        <v>118</v>
       </c>
       <c r="J3" t="n">
-        <v>80768359</v>
+        <v>10069470</v>
       </c>
       <c r="K3" t="n">
-        <v>84840916</v>
+        <v>10224579</v>
       </c>
       <c r="L3" t="n">
-        <v>97543543</v>
+        <v>11769725</v>
       </c>
       <c r="M3" t="n">
-        <v>121610614</v>
+        <v>15069868</v>
       </c>
       <c r="N3" t="n">
-        <v>130400602</v>
+        <v>16200881</v>
       </c>
       <c r="O3" t="n">
-        <v>126403554</v>
+        <v>15718651</v>
       </c>
       <c r="P3" t="n">
-        <v>129829243</v>
+        <v>16179493</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8633541464805603</v>
+        <v>0.8166744112968445</v>
       </c>
       <c r="S3" t="n">
-        <v>0.71064692735672</v>
+        <v>0.5978219509124756</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5910044312477112</v>
+        <v>0.4200646281242371</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2927136421203613</v>
+        <v>0.1159689873456955</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6531523466110229</v>
+        <v>0.444269597530365</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6916451454162598</v>
+        <v>0.4679322242736816</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38791394</v>
+        <v>4813274</v>
       </c>
       <c r="Z3" t="n">
-        <v>1596247</v>
+        <v>198388</v>
       </c>
       <c r="AA3" t="n">
-        <v>68802</v>
+        <v>8469</v>
       </c>
       <c r="AB3" t="n">
-        <v>54902</v>
+        <v>6867</v>
       </c>
       <c r="AC3" t="n">
-        <v>326</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80768952</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>89383707</v>
+        <v>11165177</v>
       </c>
       <c r="AG3" t="n">
-        <v>102923975</v>
+        <v>12815311</v>
       </c>
       <c r="AH3" t="n">
-        <v>123113659</v>
+        <v>15344357</v>
       </c>
       <c r="AI3" t="n">
-        <v>130714348</v>
+        <v>16295858</v>
       </c>
       <c r="AJ3" t="n">
-        <v>127192314</v>
+        <v>15855036</v>
       </c>
       <c r="AK3" t="n">
-        <v>130020000</v>
+        <v>16209148</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575306177139282</v>
+        <v>0.9574769735336304</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098653793334961</v>
+        <v>0.9097115993499756</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570844531059265</v>
+        <v>0.8566603064537048</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6610108613967896</v>
+        <v>0.6601800322532654</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.901400625705719</v>
+        <v>0.9011573195457458</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311955571174622</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06365506585155814</v>
+        <v>0.05376023718457842</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03192520221778363</v>
+        <v>0.03191057304788653</v>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>5912423</v>
+        <v>1077840</v>
       </c>
       <c r="E4" t="n">
-        <v>18772144</v>
+        <v>1978496</v>
       </c>
       <c r="F4" t="n">
-        <v>1475242</v>
+        <v>207419</v>
       </c>
       <c r="G4" t="n">
-        <v>87334</v>
+        <v>17790</v>
       </c>
       <c r="H4" t="n">
-        <v>152182</v>
+        <v>24978</v>
       </c>
       <c r="I4" t="n">
-        <v>16214</v>
+        <v>2982</v>
       </c>
       <c r="J4" t="n">
-        <v>593</v>
+        <v>150</v>
       </c>
       <c r="K4" t="n">
-        <v>6320773</v>
+        <v>1164382</v>
       </c>
       <c r="L4" t="n">
-        <v>7714487</v>
+        <v>1336768</v>
       </c>
       <c r="M4" t="n">
-        <v>2567215</v>
+        <v>407355</v>
       </c>
       <c r="N4" t="n">
-        <v>556096</v>
+        <v>125345</v>
       </c>
       <c r="O4" t="n">
-        <v>1188793</v>
+        <v>186416</v>
       </c>
       <c r="P4" t="n">
-        <v>296812</v>
+        <v>42917</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999942183494568</v>
+        <v>0.9999881386756897</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8550699353218079</v>
+        <v>0.7974174618721008</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7096922993659973</v>
+        <v>0.5973023772239685</v>
       </c>
       <c r="T4" t="n">
-        <v>0.611333429813385</v>
+        <v>0.453147679567337</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2830329537391663</v>
+        <v>0.09232474863529205</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6718176007270813</v>
+        <v>0.4911434054374695</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7344486117362976</v>
+        <v>0.5538896918296814</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1660174</v>
+        <v>208961</v>
       </c>
       <c r="Z4" t="n">
-        <v>24034613</v>
+        <v>3010697</v>
       </c>
       <c r="AA4" t="n">
-        <v>666659</v>
+        <v>83070</v>
       </c>
       <c r="AB4" t="n">
-        <v>44412</v>
+        <v>5580</v>
       </c>
       <c r="AC4" t="n">
-        <v>9168</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1777982</v>
+        <v>223784</v>
       </c>
       <c r="AG4" t="n">
-        <v>2334055</v>
+        <v>291182</v>
       </c>
       <c r="AH4" t="n">
-        <v>1064170</v>
+        <v>132866</v>
       </c>
       <c r="AI4" t="n">
-        <v>242350</v>
+        <v>30368</v>
       </c>
       <c r="AJ4" t="n">
-        <v>400033</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106055</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568519592285156</v>
+        <v>0.9565237760543823</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106738567352295</v>
+        <v>0.9107611775398254</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8574901223182678</v>
+        <v>0.8574357628822327</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613208055496216</v>
+        <v>0.660691499710083</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901663064956665</v>
+        <v>0.9015728235244751</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313228130340576</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="D5" t="n">
-        <v>284092</v>
+        <v>63198</v>
       </c>
       <c r="E5" t="n">
-        <v>1969561</v>
+        <v>360643</v>
       </c>
       <c r="F5" t="n">
-        <v>4430034</v>
+        <v>394347</v>
       </c>
       <c r="G5" t="n">
-        <v>192598</v>
+        <v>36679</v>
       </c>
       <c r="H5" t="n">
-        <v>560199</v>
+        <v>73363</v>
       </c>
       <c r="I5" t="n">
-        <v>59225</v>
+        <v>10504</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5535785</v>
+        <v>921585</v>
       </c>
       <c r="L5" t="n">
-        <v>7643426</v>
+        <v>1331011</v>
       </c>
       <c r="M5" t="n">
-        <v>3065737</v>
+        <v>544430</v>
       </c>
       <c r="N5" t="n">
-        <v>507055</v>
+        <v>79363</v>
       </c>
       <c r="O5" t="n">
-        <v>1415573</v>
+        <v>283941</v>
       </c>
       <c r="P5" t="n">
-        <v>477193</v>
+        <v>103003</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999954700469971</v>
+        <v>0.9999908804893494</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9099549055099487</v>
+        <v>0.8729308843612671</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8833637833595276</v>
+        <v>0.8374890685081482</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9572203159332275</v>
+        <v>0.9420208930969238</v>
       </c>
       <c r="U5" t="n">
-        <v>0.991925835609436</v>
+        <v>0.987529993057251</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9802210330963135</v>
+        <v>0.9713476300239563</v>
       </c>
       <c r="W5" t="n">
-        <v>0.994121789932251</v>
+        <v>0.9911110997200012</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>65006</v>
+        <v>8176</v>
       </c>
       <c r="Z5" t="n">
-        <v>687519</v>
+        <v>86508</v>
       </c>
       <c r="AA5" t="n">
-        <v>6424509</v>
+        <v>804213</v>
       </c>
       <c r="AB5" t="n">
-        <v>79964</v>
+        <v>10008</v>
       </c>
       <c r="AC5" t="n">
-        <v>233709</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1720517</v>
+        <v>213765</v>
       </c>
       <c r="AG5" t="n">
-        <v>2380957</v>
+        <v>298810</v>
       </c>
       <c r="AH5" t="n">
-        <v>1071262</v>
+        <v>134564</v>
       </c>
       <c r="AI5" t="n">
-        <v>243022</v>
+        <v>30507</v>
       </c>
       <c r="AJ5" t="n">
-        <v>402409</v>
+        <v>50502</v>
       </c>
       <c r="AK5" t="n">
-        <v>106478</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734305143356323</v>
+        <v>0.9733461737632751</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641916751861572</v>
+        <v>0.9640599489212036</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837824106216431</v>
+        <v>0.9837091565132141</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963138103485107</v>
+        <v>0.9962917566299438</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939058423042297</v>
+        <v>0.9938759207725525</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983859062194824</v>
+        <v>0.9983792304992676</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>105962</v>
+        <v>18003</v>
       </c>
       <c r="E6" t="n">
-        <v>143514</v>
+        <v>24056</v>
       </c>
       <c r="F6" t="n">
-        <v>166620</v>
+        <v>27291</v>
       </c>
       <c r="G6" t="n">
-        <v>209847</v>
+        <v>10411</v>
       </c>
       <c r="H6" t="n">
-        <v>81046</v>
+        <v>8649</v>
       </c>
       <c r="I6" t="n">
-        <v>9822</v>
+        <v>1352</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>52354</v>
+        <v>6591</v>
       </c>
       <c r="Z6" t="n">
-        <v>43154</v>
+        <v>5395</v>
       </c>
       <c r="AA6" t="n">
-        <v>87663</v>
+        <v>11026</v>
       </c>
       <c r="AB6" t="n">
-        <v>473880</v>
+        <v>59267</v>
       </c>
       <c r="AC6" t="n">
-        <v>56003</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="D7" t="n">
-        <v>17779</v>
+        <v>5249</v>
       </c>
       <c r="E7" t="n">
-        <v>241061</v>
+        <v>58171</v>
       </c>
       <c r="F7" t="n">
-        <v>713608</v>
+        <v>131464</v>
       </c>
       <c r="G7" t="n">
-        <v>232131</v>
+        <v>61031</v>
       </c>
       <c r="H7" t="n">
-        <v>2665680</v>
+        <v>226992</v>
       </c>
       <c r="I7" t="n">
-        <v>210839</v>
+        <v>27961</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>6487</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>238395</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60944</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3678844</v>
+        <v>460431</v>
       </c>
       <c r="AD7" t="n">
-        <v>96359</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>213</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>517</v>
+        <v>92</v>
       </c>
       <c r="E8" t="n">
-        <v>20328</v>
+        <v>5359</v>
       </c>
       <c r="F8" t="n">
-        <v>47956</v>
+        <v>12374</v>
       </c>
       <c r="G8" t="n">
-        <v>22845</v>
+        <v>7340</v>
       </c>
       <c r="H8" t="n">
-        <v>385334</v>
+        <v>77823</v>
       </c>
       <c r="I8" t="n">
-        <v>1070352</v>
+        <v>90587</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2651</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2128</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100827</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1441067</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
